--- a/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:29</t>
+          <t>2026-10-14 00:25:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:40</t>
+          <t>2026-10-14 00:25:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:51</t>
+          <t>2026-10-14 00:25:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:49</t>
+          <t>2026-10-14 01:00:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:51</t>
+          <t>2026-10-14 01:01:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:52</t>
+          <t>2026-10-14 01:01:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,38 +504,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1180</v>
+        <v>3315</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.74%2,482,000</t>
+          <t>6.47%921,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2482000</v>
+        <v>921000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3280</v>
+        <v>1185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.55%894,000</t>
+          <t>6.28%2,482,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>6.28%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>894000</v>
+        <v>2482000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5545</v>
+        <v>2490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.32%475,000</t>
+          <t>6.22%1,166,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>475000</v>
+        <v>1166000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2490</v>
+        <v>1685</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.14%1,116,000</t>
+          <t>6.11%1,663,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.11%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1116000</v>
+        <v>1663000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1715</v>
+        <v>2235</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.07%1,630,000</t>
+          <t>6.01%1,241,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1630000</v>
+        <v>1241000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2260</v>
+        <v>5520</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.92%1,161,000</t>
+          <t>5.64%475,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.64%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1161000</v>
+        <v>475000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,33 +875,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.66%1,227,000</t>
+          <t>5.49%1,255,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1227000</v>
+        <v>1255000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.65%293,000</t>
+          <t>5.04%323,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>293000</v>
+        <v>323000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,33 +997,33 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.57%344,000</t>
+          <t>4.63%364,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>344000</v>
+        <v>364000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.03%176,000</t>
+          <t>3.94%183,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>176000</v>
+        <v>183000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+3.08%134</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+3.08%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8095</v>
+        <v>134</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.40%194,000</t>
+          <t>3.52%12,620,868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>194000</v>
+        <v>12620868</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.26%130</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>130</v>
+        <v>8245</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.29%11,420,868</t>
+          <t>3.50%202,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>11420868</v>
+        <v>202000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.63%544</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.21%2,682,000</t>
+          <t>3.13%2,682,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,33 +1302,33 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.07%986,000</t>
+          <t>3.11%1,007,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>986000</v>
+        <v>1007000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:00:58</t>
+          <t>2026-10-14 22:01:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.97%7,245,000</t>
+          <t>2.90%7,245,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.39%3,645,000</t>
+          <t>2.49%3,645,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2200</v>
+        <v>2115</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.17%424,000</t>
+          <t>2.07%440,675</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>424000</v>
+        <v>440675</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2195</v>
+        <v>1050</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.17%440,675</t>
+          <t>2.03%910,013</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>440675</v>
+        <v>910013</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.46%493.5</t>
+          <t>+3.34%510</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.46%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>493.5</v>
+        <v>510</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.15%1,904,000</t>
+          <t>2.01%1,904,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1040</v>
+        <v>2250</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.97%860,013</t>
+          <t>2.01%426,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>860013</v>
+        <v>426000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.79%179,000</t>
+          <t>1.74%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,33 +1790,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.26%1,000,000</t>
+          <t>1.42%1,200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1170</v>
+        <v>747</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.96%359,000</t>
+          <t>1.20%755,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>359000</v>
+        <v>755000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1775</v>
+        <v>7070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.82%200,000</t>
+          <t>1.03%69,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>200000</v>
+        <v>69000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,34 +1968,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.39%5700</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.39%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5700</v>
+        <v>1540</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.68%52,000</t>
+          <t>0.95%278,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>52000</v>
+        <v>278000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.09%795</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>795</v>
+        <v>1260</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.67%379,000</t>
+          <t>0.90%359,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>379000</v>
+        <v>359000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-5.69%116</t>
+          <t>+7.67%856</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>+7.67%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>116</v>
+        <v>856</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.53%1,991,000</t>
+          <t>0.82%479,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1991000</v>
+        <v>479000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6990</v>
+        <v>1785</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.53%34,000</t>
+          <t>0.76%200,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>34000</v>
+        <v>200000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>-1.49%5615</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1655</v>
+        <v>5615</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.50%133,000</t>
+          <t>0.70%57,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>133000</v>
+        <v>57000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:00</t>
+          <t>2026-10-14 22:01:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1600</v>
+        <v>1735</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.49%134,000</t>
+          <t>0.65%183,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>134000</v>
+        <v>183000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,33 +2339,33 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.05%806</t>
+          <t>+5.96%854</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>806</v>
+        <v>854</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.49%267,000</t>
+          <t>0.63%367,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>267000</v>
+        <v>367000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.13%966</t>
+          <t>+0.86%117</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>966</v>
+        <v>117</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.43%201,000</t>
+          <t>0.51%2,032,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>201000</v>
+        <v>2032000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-7.69%1140</t>
+          <t>+2.48%990</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1140</v>
+        <v>990</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.42%158,000</t>
+          <t>0.43%206,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>158000</v>
+        <v>206000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+2.54%283</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>17350</v>
+        <v>283</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.42%11,000</t>
+          <t>0.41%693,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>11000</v>
+        <v>693000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.17%276</t>
+          <t>+0.28%720</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>276</v>
+        <v>720</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.42%675,000</t>
+          <t>0.41%266,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>675000</v>
+        <v>266000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>740</v>
+        <v>17500</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.42%255,000</t>
+          <t>0.41%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>255000</v>
+        <v>11000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+0.14%356</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2725</v>
+        <v>356</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.42%64,000</t>
+          <t>0.41%534,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>64000</v>
+        <v>534000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-4.27%718</t>
+          <t>+1.32%1155</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>718</v>
+        <v>1155</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.42%256,000</t>
+          <t>0.41%166,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>256000</v>
+        <v>166000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-5.56%1190</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1190</v>
+        <v>2880</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.41%149,952</t>
+          <t>0.40%69,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>149952</v>
+        <v>69000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.14%355.5</t>
+          <t>-1.68%1170</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>355.5</v>
+        <v>1170</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.40%520,000</t>
+          <t>0.39%152,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>520000</v>
+        <v>152952</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.31%175</t>
+          <t>+0.57%176</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.25%629,000</t>
+          <t>0.24%629,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:01</t>
+          <t>2026-10-14 22:01:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-6.53%2360</t>
+          <t>+0.21%2365</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.53%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2360</v>
+        <v>2365</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">

--- a/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:46</t>
+          <t>2026-10-14 22:31:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:47</t>
+          <t>2026-10-14 22:31:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:49</t>
+          <t>2026-10-14 22:31:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
